--- a/output/pdf_financials_xlsx/DOO.xlsx
+++ b/output/pdf_financials_xlsx/DOO.xlsx
@@ -2259,28 +2259,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>542.4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>298.6</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>1325.7</v>
@@ -2357,28 +2357,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>542.4</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>298.6</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1325.7</v>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">

--- a/output/pdf_financials_xlsx/DOO.xlsx
+++ b/output/pdf_financials_xlsx/DOO.xlsx
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -6099,16 +6099,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -20092,7 +20092,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -24270,7 +24274,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -24350,7 +24358,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E215" s="5" t="n">
         <v>2.6</v>
       </c>
@@ -26412,7 +26424,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E240" s="5" t="n">
         <v>-11.7</v>
       </c>

--- a/output/pdf_financials_xlsx/DOO.xlsx
+++ b/output/pdf_financials_xlsx/DOO.xlsx
@@ -3377,13 +3377,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>1603</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>1730.3</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>2003.7</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -3426,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>929.8</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>963.5</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>1098.6</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -3769,28 +3769,28 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>518.8</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>560.2</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>687.4</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>754.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>814.7</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>965.3</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>943.7</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1026.8</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
@@ -3965,28 +3965,28 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>518.8</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>560.2</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>687.4</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>754.8</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>814.7</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>965.3</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>943.7</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>1026.8</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>0</v>
@@ -4314,22 +4314,22 @@
         <v>7.3</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1588.7</v>
+        <v>901.3</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1794.4</v>
+        <v>1039.6</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2094.8</v>
+        <v>1280.1</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>2268.4</v>
+        <v>1303.1</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2338.6</v>
+        <v>1394.9</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2357.1</v>
+        <v>1330.3</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>7.6</v>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>70.3</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>177.1</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>0</v>
@@ -5918,13 +5918,13 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0</v>
+        <v>116.3</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>0</v>
+        <v>193.4</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0</v>
+        <v>238.2</v>
       </c>
     </row>
     <row r="109">
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -6941,10 +6941,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>221.6</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>-554.5</v>
@@ -6967,25 +6965,17 @@
       <c r="I129" s="3" t="n">
         <v>-177.7</v>
       </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J129" s="3" t="n">
+        <v>589.3</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>-1142.2</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>-793.7</v>
       </c>
       <c r="N129" s="3" t="n">
         <v>-553.1</v>
@@ -7253,10 +7243,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>301.7</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>80.40000000000001</v>
@@ -7279,31 +7267,23 @@
       <c r="I135" s="3" t="n">
         <v>274.8</v>
       </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" s="3" t="n">
+        <v>700.9</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>1109.7</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>270.2</v>
+        <v>291.6</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>931</v>
+        <v>914.8</v>
       </c>
     </row>
   </sheetData>
@@ -18996,7 +18976,11 @@
           <t>Impairment charge 25,32</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -19954,7 +19938,11 @@
           <t>Net cash flows generated from operating activities</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>444.8</v>
       </c>
@@ -21772,7 +21760,11 @@
           <t>Impairment charge 26</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -23784,7 +23776,11 @@
           <t>Impairment charge 25</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -27390,7 +27386,11 @@
           <t>Impairment charge 22</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -28236,7 +28236,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>-1.1</v>
       </c>
@@ -30908,7 +30912,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -31724,7 +31732,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -32868,7 +32880,11 @@
           <t>Income taxes recovery</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E318" s="5" t="n">
         <v>-0.4</v>
       </c>
